--- a/study/ilab_experiments.xlsx
+++ b/study/ilab_experiments.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T00:44:21</t>
+          <t>2026-10-07T01:04:22</t>
         </is>
       </c>
     </row>
@@ -57853,36 +57853,36 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>51.9</v>
+        <v>60.5</v>
       </c>
       <c r="F2" t="n">
-        <v>61.7</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>9.9</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>crash 9, fired after a pass 1, timeout 5</t>
+          <t>fired after a pass 1, timeout 5</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4.67</v>
+        <v>1.67</v>
       </c>
       <c r="K2" t="n">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0247</v>
+        <v>0.0581</v>
       </c>
       <c r="N2" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="3">
@@ -57903,36 +57903,36 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>59.3</v>
+        <v>61.7</v>
       </c>
       <c r="F3" t="n">
-        <v>60.5</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
         <v>1.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>crash 4, timeout 1</t>
+          <t>timeout 2</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="K3" t="n">
         <v>0.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0204</v>
+        <v>0.0091</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0612</v>
+        <v>0.0273</v>
       </c>
       <c r="N3" t="n">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="4">
@@ -57953,36 +57953,30 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>49.4</v>
+        <v>54.3</v>
       </c>
       <c r="F4" t="n">
         <v>54.3</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>crash 7</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.0169</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -58003,36 +57997,30 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>60.5</v>
+        <v>64.2</v>
       </c>
       <c r="F5" t="n">
-        <v>61.7</v>
+        <v>64.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>crash 4, timeout 1</t>
+          <t>timeout 1</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="K5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0205</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.31</v>
+        <v>0.0057</v>
       </c>
     </row>
   </sheetData>

--- a/study/ilab_experiments.xlsx
+++ b/study/ilab_experiments.xlsx
@@ -12,22 +12,24 @@
     <sheet name="Task x harness" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Strategies" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="K-fold" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Fallback" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Task features" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Router picks" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Failures" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Older runs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Qwen vs Luna" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Fallback" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Task features" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Router picks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Failures" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Older runs" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Phase1 runs'!$A$1:$Y$454</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Task x harness'!$A$1:$I$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Task x harness'!$A$1:$I$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Strategies'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'K-fold'!$A$1:$P$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fallback'!$A$1:$N$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Task features'!$A$1:$W$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Router picks'!$A$1:$J$361</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Failures'!$A$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Older runs'!$A$1:$U$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'K-fold'!$A$1:$Q$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Qwen vs Luna'!$A$1:$K$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fallback'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Task features'!$A$1:$W$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Router picks'!$A$1:$J$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Failures'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Older runs'!$A$1:$U$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -464,7 +466,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T01:04:22</t>
+          <t>2026-10-07T15:42:50</t>
         </is>
       </c>
     </row>
@@ -476,7 +478,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SEALED: test-set rewards are hidden</t>
+          <t>UNSEALED. The 18 test tasks were held back to measure generalisation, then deliberately unsealed so the deployment lookup could hard-code the best harness for all 45 tasks. All of them are training data now and none of them can measure generalisation any more; the 44 Phase 2 tasks are the held-out set. study/test_unseal_log.jsonl records every unsealing.</t>
         </is>
       </c>
     </row>
@@ -642,65 +644,101 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Phase1 runs: one row per attempt | Task x harness: per-cell pass rates | Strategies: single dev/test split | K-fold: cross-validated scores, the main evaluation | Fallback: retry on an observable failure, with the same-harness control | Task features: task.toml metadata and keyword flags | Router picks: every pick with reason | Failures: broken attempts by harness | Older runs: pre-study jobs</t>
+          <t>Phase1 runs: one row per attempt | Task x harness: per-cell pass rates | Strategies: single dev/test split | K-fold: cross-validated scores, the main evaluation | Qwen vs Luna: lookup-vs-oracle check and how well a different model's run predicts Luna's | Fallback: retry on an observable failure, with the same-harness control | Task features: task.toml metadata and keyword flags | Router picks: every pick with reason | Failures: broken attempts by harness | Older runs: pre-study jobs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Read K-fold, not Strategies</t>
+          <t>Deployment lookup</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Strategies scores one dev/test split and lets a strategy that learned from those same tasks look perfect. K-fold refits anything learned on the training folds only. Use baseline_mode='fixed' rows for claims: 'fold' re-picks the best single harness per fold and is itself unstable, which flatters every strategy.</t>
+          <t>router/success_table.json, frozen at sha256=c7f5166b6d395def, Table A covers 45 tasks. table_router.lookup() answers those from the table with no model call and reaches the best-of-3-harnesses oracle on them by construction (70.4% pass against 54.8% for always mini-swe-agent). That is memorisation, not generalisation: an unlisted task gets the Qwen fallback or the default harness.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Fallback: read the control</t>
+          <t>Qwen as a fallback hint</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>gain_same_harness_retry_pts is what simply rerunning the same harness achieves. Most triggers are infrastructure crashes, so a switch only earns credit where it beats that column. For mini-swe-agent it does not.</t>
+          <t>Qwen3-Coder's 89-task run does predict Luna: Luna passes 36.3 points more often with a harness Qwen passed with, and when Qwen passes at all its harness is Luna's best one 76% of the time against 33% by chance. But as a fallback rule it only changes the pick on 5 of the 45 tasks and gains 2.2 points, CI [-2.2, +7.4], so it is unproven. lookup() uses it anyway as a judgement call: it leans positive, is cheaper per pass, and changes only 2 of the 44 unrun tasks. It also skips harnesses that could not install for the task in the Qwen run.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Harness versions</t>
+          <t>K-fold task pools</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Phase 1 mixes pi 1.0.0/1.0.1/1.0.2 (terminus-2 2.0.0 and mini-swe-agent 2.4.6 were stable), so 'pi' is not one harness here. Future runs pin the version via run_phase1.sh.</t>
+          <t>task_pool='dev' is the original 27-task evaluation; 'all' adds the unsealed test tasks (44 of 45 - qemu-startup is excluded because only terminus-2 ever ran it, so no strategy has a real choice there).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Column: reward</t>
+          <t>Read K-fold, not Strategies</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1 = task solved, 0 = not solved, blank = run broke before grading, 'sealed' = hidden test result</t>
+          <t>Strategies scores one dev/test split and lets a strategy that learned from those same tasks look perfect. K-fold refits anything learned on the training folds only. Use baseline_mode='fixed' rows for claims: 'fold' re-picks the best single harness per fold and is itself unstable, which flatters every strategy.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>Fallback: read the control</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>gain_same_harness_retry_pts is what simply rerunning the same harness achieves. Most triggers are infrastructure crashes, so a switch only earns credit where it beats that column. For mini-swe-agent it does not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Harness versions</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1 mixes pi 1.0.0/1.0.1/1.0.2 (terminus-2 2.0.0 and mini-swe-agent 2.4.6 were stable), so 'pi' is not one harness here. Future runs pin the version via run_phase1.sh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Column: reward</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1 = task solved, 0 = not solved, blank = run broke before grading</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
           <t>Column: times</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Minutes. env_setup = container start, agent_setup = harness install, agent_run = the agent working, verifier = grading.</t>
         </is>
@@ -717,7 +755,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U133"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>harness</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>error_type</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>attempts_failed</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>share_of_harness_attempts_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AgentSetupTimeoutError</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NonZeroAgentExitCodeError</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RuntimeError</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NonZeroAgentExitCodeError</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RuntimeError</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VerifierTimeoutError</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>APIError</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RuntimeError</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VerifierTimeoutError</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TOTAL (any error)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TOTAL (any error)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TOTAL (any error)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -11033,8 +11330,162 @@
         <v>0.18</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>live-lookup-fix-git-20261007-144735</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>pre-study (not part of Phase 1)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>fix-git__vuW7uUW</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>fix-git</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2.0.0</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.6-luna</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>9303</v>
+      </c>
+      <c r="L134" t="n">
+        <v>3075</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1164</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.00297905</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>2026-10-07T03:47:42.655720Z</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>2026-10-07T03:49:04.127765Z</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>live-lookup-fix-git-20261007-150213</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>pre-study (not part of Phase 1)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>fix-git__XyZfYPi</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>fix-git</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2.0.0</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.6-luna</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>15469</v>
+      </c>
+      <c r="L135" t="n">
+        <v>10057</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1942</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.00384799</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>2026-10-07T04:02:18.089056Z</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>2026-10-07T04:03:30.185250Z</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U133"/>
+  <autoFilter ref="A1:U135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35288,10 +35739,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J267" t="n">
+        <v>1</v>
       </c>
       <c r="M267" t="n">
         <v>181582</v>
@@ -35381,10 +35830,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J268" t="n">
+        <v>0</v>
       </c>
       <c r="M268" t="n">
         <v>50594</v>
@@ -35474,10 +35921,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J269" t="n">
+        <v>0</v>
       </c>
       <c r="M269" t="n">
         <v>282900</v>
@@ -35567,10 +36012,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J270" t="n">
+        <v>1</v>
       </c>
       <c r="M270" t="n">
         <v>657168</v>
@@ -35660,10 +36103,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J271" t="n">
+        <v>1</v>
       </c>
       <c r="M271" t="n">
         <v>421590</v>
@@ -35753,10 +36194,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J272" t="n">
+        <v>1</v>
       </c>
       <c r="M272" t="n">
         <v>228466</v>
@@ -35846,10 +36285,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J273" t="n">
+        <v>1</v>
       </c>
       <c r="M273" t="n">
         <v>157009</v>
@@ -35939,10 +36376,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J274" t="n">
+        <v>1</v>
       </c>
       <c r="M274" t="n">
         <v>474197</v>
@@ -36032,10 +36467,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J275" t="n">
+        <v>1</v>
       </c>
       <c r="M275" t="n">
         <v>433089</v>
@@ -36125,10 +36558,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J276" t="n">
+        <v>1</v>
       </c>
       <c r="M276" t="n">
         <v>505097</v>
@@ -36218,10 +36649,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J277" t="n">
+        <v>1</v>
       </c>
       <c r="M277" t="n">
         <v>250512</v>
@@ -36311,10 +36740,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J278" t="n">
+        <v>0</v>
       </c>
       <c r="M278" t="n">
         <v>923587</v>
@@ -36404,10 +36831,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J279" t="n">
+        <v>1</v>
       </c>
       <c r="M279" t="n">
         <v>1006361</v>
@@ -36497,10 +36922,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J280" t="n">
+        <v>0</v>
       </c>
       <c r="M280" t="n">
         <v>805890</v>
@@ -36590,10 +37013,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J281" t="n">
+        <v>0</v>
       </c>
       <c r="M281" t="n">
         <v>635475</v>
@@ -36683,10 +37104,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J282" t="n">
+        <v>0</v>
       </c>
       <c r="M282" t="n">
         <v>1225069</v>
@@ -36776,10 +37195,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J283" t="n">
+        <v>1</v>
       </c>
       <c r="M283" t="n">
         <v>1129520</v>
@@ -36953,10 +37370,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J285" t="n">
+        <v>0</v>
       </c>
       <c r="M285" t="n">
         <v>4586200</v>
@@ -37046,10 +37461,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J286" t="n">
+        <v>1</v>
       </c>
       <c r="M286" t="n">
         <v>72329</v>
@@ -37139,10 +37552,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J287" t="n">
+        <v>1</v>
       </c>
       <c r="M287" t="n">
         <v>95787</v>
@@ -37313,10 +37724,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J289" t="n">
+        <v>1</v>
       </c>
       <c r="M289" t="n">
         <v>49567</v>
@@ -37406,10 +37815,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J290" t="n">
+        <v>1</v>
       </c>
       <c r="M290" t="n">
         <v>55755</v>
@@ -37503,10 +37910,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J291" t="n">
+        <v>1</v>
       </c>
       <c r="M291" t="n">
         <v>162141</v>
@@ -37596,10 +38001,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J292" t="n">
+        <v>1</v>
       </c>
       <c r="M292" t="n">
         <v>49206</v>
@@ -37689,10 +38092,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J293" t="n">
+        <v>1</v>
       </c>
       <c r="M293" t="n">
         <v>54822</v>
@@ -37863,10 +38264,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J295" t="n">
+        <v>1</v>
       </c>
       <c r="M295" t="n">
         <v>81051</v>
@@ -37956,10 +38355,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J296" t="n">
+        <v>1</v>
       </c>
       <c r="M296" t="n">
         <v>87058</v>
@@ -38049,10 +38446,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J297" t="n">
+        <v>1</v>
       </c>
       <c r="M297" t="n">
         <v>425066</v>
@@ -38142,10 +38537,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J298" t="n">
+        <v>0</v>
       </c>
       <c r="M298" t="n">
         <v>27044</v>
@@ -38235,10 +38628,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J299" t="n">
+        <v>0</v>
       </c>
       <c r="M299" t="n">
         <v>19868</v>
@@ -38328,10 +38719,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J300" t="n">
+        <v>0</v>
       </c>
       <c r="M300" t="n">
         <v>32470</v>
@@ -38421,10 +38810,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J301" t="n">
+        <v>0</v>
       </c>
       <c r="M301" t="n">
         <v>7579</v>
@@ -38514,10 +38901,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J302" t="n">
+        <v>0</v>
       </c>
       <c r="M302" t="n">
         <v>8133</v>
@@ -38607,10 +38992,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J303" t="n">
+        <v>0</v>
       </c>
       <c r="M303" t="n">
         <v>24551</v>
@@ -38700,10 +39083,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J304" t="n">
+        <v>0</v>
       </c>
       <c r="M304" t="n">
         <v>5400</v>
@@ -38793,10 +39174,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J305" t="n">
+        <v>0</v>
       </c>
       <c r="M305" t="n">
         <v>18089</v>
@@ -38886,10 +39265,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J306" t="n">
+        <v>0</v>
       </c>
       <c r="M306" t="n">
         <v>5556</v>
@@ -38979,10 +39356,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J307" t="n">
+        <v>0</v>
       </c>
       <c r="M307" t="n">
         <v>681215</v>
@@ -39072,10 +39447,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J308" t="n">
+        <v>0</v>
       </c>
       <c r="M308" t="n">
         <v>1187420</v>
@@ -39165,10 +39538,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J309" t="n">
+        <v>0</v>
       </c>
       <c r="M309" t="n">
         <v>367696</v>
@@ -39258,10 +39629,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J310" t="n">
+        <v>1</v>
       </c>
       <c r="M310" t="n">
         <v>550623</v>
@@ -39351,10 +39720,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J311" t="n">
+        <v>1</v>
       </c>
       <c r="M311" t="n">
         <v>460988</v>
@@ -39444,10 +39811,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J312" t="n">
+        <v>1</v>
       </c>
       <c r="M312" t="n">
         <v>2177154</v>
@@ -39537,10 +39902,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J313" t="n">
+        <v>1</v>
       </c>
       <c r="M313" t="n">
         <v>8538176</v>
@@ -39630,10 +39993,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J314" t="n">
+        <v>1</v>
       </c>
       <c r="M314" t="n">
         <v>3627404</v>
@@ -39723,10 +40084,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J315" t="n">
+        <v>1</v>
       </c>
       <c r="M315" t="n">
         <v>3426034</v>
@@ -39816,10 +40175,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J316" t="n">
+        <v>1</v>
       </c>
       <c r="M316" t="n">
         <v>57745</v>
@@ -39909,10 +40266,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J317" t="n">
+        <v>0</v>
       </c>
       <c r="M317" t="n">
         <v>49389</v>
@@ -40002,10 +40357,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J318" t="n">
+        <v>1</v>
       </c>
       <c r="M318" t="n">
         <v>83201</v>
@@ -40095,10 +40448,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J319" t="n">
+        <v>1</v>
       </c>
       <c r="M319" t="n">
         <v>120520</v>
@@ -40188,10 +40539,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J320" t="n">
+        <v>1</v>
       </c>
       <c r="M320" t="n">
         <v>140162</v>
@@ -40281,10 +40630,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J321" t="n">
+        <v>1</v>
       </c>
       <c r="M321" t="n">
         <v>58834</v>
@@ -40374,10 +40721,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J322" t="n">
+        <v>0</v>
       </c>
       <c r="M322" t="n">
         <v>12737</v>
@@ -40548,10 +40893,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J324" t="n">
+        <v>0</v>
       </c>
       <c r="M324" t="n">
         <v>104418</v>
@@ -40641,10 +40984,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J325" t="n">
+        <v>0</v>
       </c>
       <c r="M325" t="n">
         <v>5221</v>
@@ -40815,10 +41156,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J327" t="n">
+        <v>1</v>
       </c>
       <c r="M327" t="n">
         <v>10560</v>
@@ -40908,10 +41247,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J328" t="n">
+        <v>1</v>
       </c>
       <c r="M328" t="n">
         <v>10864</v>
@@ -41001,10 +41338,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J329" t="n">
+        <v>1</v>
       </c>
       <c r="M329" t="n">
         <v>7517</v>
@@ -41094,10 +41429,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J330" t="n">
+        <v>1</v>
       </c>
       <c r="M330" t="n">
         <v>15618</v>
@@ -41187,10 +41520,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J331" t="n">
+        <v>1</v>
       </c>
       <c r="M331" t="n">
         <v>17548</v>
@@ -41280,10 +41611,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J332" t="n">
+        <v>1</v>
       </c>
       <c r="M332" t="n">
         <v>12978</v>
@@ -41373,10 +41702,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J333" t="n">
+        <v>1</v>
       </c>
       <c r="M333" t="n">
         <v>4044</v>
@@ -41466,10 +41793,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J334" t="n">
+        <v>1</v>
       </c>
       <c r="M334" t="n">
         <v>3991</v>
@@ -41559,10 +41884,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J335" t="n">
+        <v>1</v>
       </c>
       <c r="M335" t="n">
         <v>3787</v>
@@ -41652,10 +41975,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J336" t="n">
+        <v>0</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
@@ -41755,10 +42076,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J337" t="n">
+        <v>0</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
@@ -41858,10 +42177,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J338" t="n">
+        <v>0</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
@@ -41961,10 +42278,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J339" t="n">
+        <v>0</v>
       </c>
       <c r="M339" t="n">
         <v>654193</v>
@@ -42135,10 +42450,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J341" t="n">
+        <v>0</v>
       </c>
       <c r="M341" t="n">
         <v>723975</v>
@@ -42228,10 +42541,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J342" t="n">
+        <v>1</v>
       </c>
       <c r="M342" t="n">
         <v>2050452</v>
@@ -42420,10 +42731,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J344" t="n">
+        <v>0</v>
       </c>
       <c r="M344" t="n">
         <v>58788</v>
@@ -42513,10 +42822,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J345" t="n">
+        <v>1</v>
       </c>
       <c r="M345" t="n">
         <v>377410</v>
@@ -42606,10 +42913,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J346" t="n">
+        <v>1</v>
       </c>
       <c r="M346" t="n">
         <v>404488</v>
@@ -42699,10 +43004,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J347" t="n">
+        <v>0</v>
       </c>
       <c r="M347" t="n">
         <v>636747</v>
@@ -42792,10 +43095,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J348" t="n">
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>408293</v>
@@ -42885,10 +43186,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J349" t="n">
+        <v>0</v>
       </c>
       <c r="M349" t="n">
         <v>831500</v>
@@ -42978,10 +43277,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J350" t="n">
+        <v>0</v>
       </c>
       <c r="M350" t="n">
         <v>750424</v>
@@ -43071,10 +43368,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J351" t="n">
+        <v>0</v>
       </c>
       <c r="M351" t="n">
         <v>607932</v>
@@ -43164,10 +43459,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J352" t="n">
+        <v>0</v>
       </c>
       <c r="M352" t="n">
         <v>542305</v>
@@ -43257,10 +43550,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J353" t="n">
+        <v>0</v>
       </c>
       <c r="M353" t="n">
         <v>2455112</v>
@@ -43350,10 +43641,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J354" t="n">
+        <v>0</v>
       </c>
       <c r="M354" t="n">
         <v>1324116</v>
@@ -43443,10 +43732,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J355" t="n">
+        <v>0</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
@@ -43627,10 +43914,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J357" t="n">
+        <v>1</v>
       </c>
       <c r="M357" t="n">
         <v>1554385</v>
@@ -43720,10 +44005,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J358" t="n">
+        <v>0</v>
       </c>
       <c r="M358" t="n">
         <v>533689</v>
@@ -43813,10 +44096,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J359" t="n">
+        <v>1</v>
       </c>
       <c r="M359" t="n">
         <v>1904821</v>
@@ -43906,10 +44187,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J360" t="n">
+        <v>0</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
@@ -44009,10 +44288,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J361" t="n">
+        <v>0</v>
       </c>
       <c r="K361" t="inlineStr">
         <is>
@@ -44112,10 +44389,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J362" t="n">
+        <v>0</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
@@ -44215,10 +44490,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J363" t="n">
+        <v>0</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
@@ -44318,10 +44591,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J364" t="n">
+        <v>0</v>
       </c>
       <c r="K364" t="inlineStr">
         <is>
@@ -44421,10 +44692,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J365" t="n">
+        <v>0</v>
       </c>
       <c r="K365" t="inlineStr">
         <is>
@@ -44524,10 +44793,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J366" t="n">
+        <v>0</v>
       </c>
       <c r="M366" t="n">
         <v>26386</v>
@@ -44617,10 +44884,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J367" t="n">
+        <v>1</v>
       </c>
       <c r="M367" t="n">
         <v>78878</v>
@@ -44791,10 +45056,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J369" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J369" t="n">
+        <v>0</v>
       </c>
       <c r="M369" t="n">
         <v>128519</v>
@@ -44884,10 +45147,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J370" t="n">
+        <v>0</v>
       </c>
       <c r="M370" t="n">
         <v>16440</v>
@@ -44977,10 +45238,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J371" t="n">
+        <v>0</v>
       </c>
       <c r="M371" t="n">
         <v>18221</v>
@@ -45070,10 +45329,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J372" t="n">
+        <v>0</v>
       </c>
       <c r="M372" t="n">
         <v>31201</v>
@@ -45163,10 +45420,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J373" t="n">
+        <v>0</v>
       </c>
       <c r="M373" t="n">
         <v>12238</v>
@@ -45256,10 +45511,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J374" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J374" t="n">
+        <v>0</v>
       </c>
       <c r="M374" t="n">
         <v>34342</v>
@@ -45349,10 +45602,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J375" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J375" t="n">
+        <v>0</v>
       </c>
       <c r="M375" t="n">
         <v>27597</v>
@@ -45442,10 +45693,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J376" t="n">
+        <v>1</v>
       </c>
       <c r="M376" t="n">
         <v>12048</v>
@@ -45535,10 +45784,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J377" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J377" t="n">
+        <v>1</v>
       </c>
       <c r="M377" t="n">
         <v>15662</v>
@@ -45628,10 +45875,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J378" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J378" t="n">
+        <v>1</v>
       </c>
       <c r="M378" t="n">
         <v>13032</v>
@@ -45721,10 +45966,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J379" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J379" t="n">
+        <v>1</v>
       </c>
       <c r="M379" t="n">
         <v>11402</v>
@@ -45814,10 +46057,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J380" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J380" t="n">
+        <v>1</v>
       </c>
       <c r="M380" t="n">
         <v>11644</v>
@@ -45907,10 +46148,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J381" t="n">
+        <v>1</v>
       </c>
       <c r="M381" t="n">
         <v>11796</v>
@@ -46000,10 +46239,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J382" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J382" t="n">
+        <v>1</v>
       </c>
       <c r="M382" t="n">
         <v>4404</v>
@@ -46093,10 +46330,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J383" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J383" t="n">
+        <v>0</v>
       </c>
       <c r="M383" t="n">
         <v>16749</v>
@@ -46186,10 +46421,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J384" t="n">
+        <v>1</v>
       </c>
       <c r="M384" t="n">
         <v>10760</v>
@@ -46279,10 +46512,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J385" t="n">
+        <v>1</v>
       </c>
       <c r="M385" t="n">
         <v>12107</v>
@@ -46372,10 +46603,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J386" t="n">
+        <v>1</v>
       </c>
       <c r="M386" t="n">
         <v>7783</v>
@@ -46465,10 +46694,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J387" t="n">
+        <v>1</v>
       </c>
       <c r="M387" t="n">
         <v>8050</v>
@@ -46558,10 +46785,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J388" t="n">
+        <v>1</v>
       </c>
       <c r="M388" t="n">
         <v>7177</v>
@@ -46651,10 +46876,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J389" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J389" t="n">
+        <v>1</v>
       </c>
       <c r="M389" t="n">
         <v>1450</v>
@@ -46744,10 +46967,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J390" t="n">
+        <v>1</v>
       </c>
       <c r="M390" t="n">
         <v>3795</v>
@@ -46837,10 +47058,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J391" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J391" t="n">
+        <v>0</v>
       </c>
       <c r="M391" t="n">
         <v>4233</v>
@@ -46930,10 +47149,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J392" t="n">
+        <v>1</v>
       </c>
       <c r="M392" t="n">
         <v>4253</v>
@@ -47023,10 +47240,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J393" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J393" t="n">
+        <v>1</v>
       </c>
       <c r="M393" t="n">
         <v>3832</v>
@@ -47116,10 +47331,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J394" t="n">
+        <v>1</v>
       </c>
       <c r="M394" t="n">
         <v>114467</v>
@@ -47209,10 +47422,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J395" t="n">
+        <v>0</v>
       </c>
       <c r="M395" t="n">
         <v>426649</v>
@@ -47302,10 +47513,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J396" t="n">
+        <v>1</v>
       </c>
       <c r="M396" t="n">
         <v>120382</v>
@@ -47395,10 +47604,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J397" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J397" t="n">
+        <v>0</v>
       </c>
       <c r="M397" t="n">
         <v>603065</v>
@@ -47488,10 +47695,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J398" t="n">
+        <v>0</v>
       </c>
       <c r="M398" t="n">
         <v>55092</v>
@@ -47581,10 +47786,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J399" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J399" t="n">
+        <v>1</v>
       </c>
       <c r="M399" t="n">
         <v>92717</v>
@@ -47674,10 +47877,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J400" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J400" t="n">
+        <v>1</v>
       </c>
       <c r="M400" t="n">
         <v>112758</v>
@@ -47767,10 +47968,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J401" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J401" t="n">
+        <v>1</v>
       </c>
       <c r="M401" t="n">
         <v>187757</v>
@@ -47860,10 +48059,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J402" t="n">
+        <v>1</v>
       </c>
       <c r="M402" t="n">
         <v>134168</v>
@@ -48034,10 +48231,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J404" t="n">
+        <v>1</v>
       </c>
       <c r="M404" t="n">
         <v>54060</v>
@@ -48127,10 +48322,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J405" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J405" t="n">
+        <v>0</v>
       </c>
       <c r="M405" t="n">
         <v>55001</v>
@@ -48301,10 +48494,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J407" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J407" t="n">
+        <v>0</v>
       </c>
       <c r="M407" t="n">
         <v>45519</v>
@@ -48394,10 +48585,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J408" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J408" t="n">
+        <v>0</v>
       </c>
       <c r="M408" t="n">
         <v>49444</v>
@@ -48487,10 +48676,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J409" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J409" t="n">
+        <v>1</v>
       </c>
       <c r="M409" t="n">
         <v>91405</v>
@@ -48580,10 +48767,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J410" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J410" t="n">
+        <v>0</v>
       </c>
       <c r="M410" t="n">
         <v>53252</v>
@@ -48673,10 +48858,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J411" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J411" t="n">
+        <v>0</v>
       </c>
       <c r="M411" t="n">
         <v>61449</v>
@@ -48766,10 +48949,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J412" t="n">
+        <v>1</v>
       </c>
       <c r="M412" t="n">
         <v>80547</v>
@@ -48859,10 +49040,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J413" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J413" t="n">
+        <v>1</v>
       </c>
       <c r="M413" t="n">
         <v>77244</v>
@@ -50464,10 +50643,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J432" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J432" t="n">
+        <v>0</v>
       </c>
       <c r="M432" t="n">
         <v>2393</v>
@@ -50561,10 +50738,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J433" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J433" t="n">
+        <v>0</v>
       </c>
       <c r="M433" t="n">
         <v>8822</v>
@@ -50658,10 +50833,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J434" t="n">
+        <v>0</v>
       </c>
       <c r="M434" t="n">
         <v>12544</v>
@@ -50755,10 +50928,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J435" t="n">
+        <v>0</v>
       </c>
       <c r="M435" t="n">
         <v>26970</v>
@@ -50848,10 +51019,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J436" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J436" t="n">
+        <v>1</v>
       </c>
       <c r="M436" t="n">
         <v>29430</v>
@@ -51022,10 +51191,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J438" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J438" t="n">
+        <v>0</v>
       </c>
       <c r="M438" t="n">
         <v>44007</v>
@@ -51115,10 +51282,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J439" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J439" t="n">
+        <v>0</v>
       </c>
       <c r="M439" t="n">
         <v>30468</v>
@@ -51212,10 +51377,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J440" t="n">
+        <v>0</v>
       </c>
       <c r="M440" t="n">
         <v>32209</v>
@@ -51305,10 +51468,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J441" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J441" t="n">
+        <v>0</v>
       </c>
       <c r="M441" t="n">
         <v>44104</v>
@@ -51398,10 +51559,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J442" t="n">
+        <v>0</v>
       </c>
       <c r="M442" t="n">
         <v>52346</v>
@@ -51491,10 +51650,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J443" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J443" t="n">
+        <v>0</v>
       </c>
       <c r="M443" t="n">
         <v>59859</v>
@@ -51584,10 +51741,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J444" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J444" t="n">
+        <v>0</v>
       </c>
       <c r="M444" t="n">
         <v>73608</v>
@@ -51677,10 +51832,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J445" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J445" t="n">
+        <v>0</v>
       </c>
       <c r="M445" t="n">
         <v>12306</v>
@@ -51770,10 +51923,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J446" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J446" t="n">
+        <v>0</v>
       </c>
       <c r="M446" t="n">
         <v>414322</v>
@@ -51863,10 +52014,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J447" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J447" t="n">
+        <v>0</v>
       </c>
       <c r="M447" t="n">
         <v>55695</v>
@@ -51956,10 +52105,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J448" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J448" t="n">
+        <v>0</v>
       </c>
       <c r="M448" t="n">
         <v>20076</v>
@@ -52049,10 +52196,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J449" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J449" t="n">
+        <v>0</v>
       </c>
       <c r="M449" t="n">
         <v>695964</v>
@@ -52142,10 +52287,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J450" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J450" t="n">
+        <v>0</v>
       </c>
       <c r="M450" t="n">
         <v>1350569</v>
@@ -52235,10 +52378,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J451" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J451" t="n">
+        <v>0</v>
       </c>
       <c r="M451" t="n">
         <v>302222</v>
@@ -52328,10 +52469,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J452" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J452" t="n">
+        <v>0</v>
       </c>
       <c r="K452" t="inlineStr">
         <is>
@@ -52431,10 +52570,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J453" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J453" t="n">
+        <v>0</v>
       </c>
       <c r="M453" t="n">
         <v>4506240</v>
@@ -52524,10 +52661,8 @@
           <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="J454" t="inlineStr">
-        <is>
-          <t>sealed</t>
-        </is>
+      <c r="J454" t="n">
+        <v>0</v>
       </c>
       <c r="M454" t="n">
         <v>4874995</v>
@@ -52585,7 +52720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -55643,8 +55778,1895 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>adaptive-rejection-sampler</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="H83" t="n">
+        <v>8</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>adaptive-rejection-sampler</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="H84" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>adaptive-rejection-sampler</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="H85" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>build-pov-ray</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="H86" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>build-pov-ray</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>build-pov-ray</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="H88" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>custom-memory-heap-crash</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>custom-memory-heap-crash</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>custom-memory-heap-crash</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="H91" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>filter-js-from-html</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H92" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>filter-js-from-html</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H93" t="n">
+        <v>25</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>filter-js-from-html</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="H94" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>fix-ocaml-gc</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="H95" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>fix-ocaml-gc</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="H96" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>fix-ocaml-gc</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="H97" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>git-multibranch</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>git-multibranch</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="H99" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>git-multibranch</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="H100" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>kv-store-grpc</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>kv-store-grpc</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>kv-store-grpc</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>3</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>mailman</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="H104" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>mailman</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="H105" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>mailman</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="H106" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>make-mips-interpreter</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="H107" t="n">
+        <v>8</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>make-mips-interpreter</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="H108" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>make-mips-interpreter</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="H109" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>mcmc-sampling-stan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="H110" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>mcmc-sampling-stan</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="H111" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>mcmc-sampling-stan</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="H112" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>model-extraction-relu-logits</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="H113" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>model-extraction-relu-logits</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>model-extraction-relu-logits</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>modernize-scientific-stack</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="H116" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>modernize-scientific-stack</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>3</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>modernize-scientific-stack</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>openssl-selfsigned-cert</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>openssl-selfsigned-cert</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>openssl-selfsigned-cert</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>overfull-hbox</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="H122" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>overfull-hbox</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="H123" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>overfull-hbox</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="H124" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>portfolio-optimization</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H125" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>portfolio-optimization</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H126" t="n">
+        <v>10</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>portfolio-optimization</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="H127" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>query-optimize</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="H128" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>query-optimize</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="H129" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>query-optimize</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H130" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>regex-chess</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="H131" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>regex-chess</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="H132" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>regex-chess</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>3</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="H133" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I82"/>
+  <autoFilter ref="A1:I133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -56333,104 +58355,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>task_pool</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
           <t>baseline_mode</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>folds</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>tasks_scored</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>pass_rate_pct</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>diff_vs_baseline_pts</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>ci95_low</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>ci95_high</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>headroom_recovered_pct</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>total_cost_usd</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>cost_per_pass_usd</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>cost_per_pass_change_pct</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>routing_cost_usd</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>meets_pass_criterion</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>meets_cost_criterion</t>
         </is>
@@ -56439,82 +58467,89 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>always terminus-2</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>27</v>
-      </c>
       <c r="F2" t="n">
-        <v>60.5</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.2</v>
+        <v>55.3</v>
       </c>
       <c r="H2" t="n">
-        <v>-11.1</v>
+        <v>-0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>8.6</v>
+        <v>-11.4</v>
       </c>
       <c r="J2" t="n">
-        <v>-9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6791</v>
+        <v>-5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0416</v>
+        <v>1.462</v>
       </c>
       <c r="M2" t="n">
-        <v>85.90000000000001</v>
+        <v>0.0601</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="b">
+        <v>133.7</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>always mini-swe-agent</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>27</v>
-      </c>
       <c r="F3" t="n">
-        <v>61.7</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>56.1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -56526,1219 +58561,3330 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3727</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0224</v>
+        <v>0.6341</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.0257</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="b">
+      <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>always pi</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>27</v>
-      </c>
       <c r="F4" t="n">
-        <v>54.3</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.4</v>
+        <v>52.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-21</v>
+        <v>-3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4</v>
+        <v>-15.2</v>
       </c>
       <c r="J4" t="n">
-        <v>-55</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3137</v>
+        <v>-24</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0214</v>
+        <v>0.6167</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.4</v>
+        <v>0.0268</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="b">
+        <v>4.3</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
       </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>27</v>
-      </c>
       <c r="F5" t="n">
-        <v>58.8</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.9</v>
+        <v>54.5</v>
       </c>
       <c r="H5" t="n">
-        <v>-9.9</v>
+        <v>-1.5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>-7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>-21</v>
+        <v>5.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4552</v>
+        <v>-10</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0286</v>
+        <v>0.9043</v>
       </c>
       <c r="M5" t="n">
-        <v>28.1</v>
+        <v>0.0377</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="b">
+        <v>46.6</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>perfect picking</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>27</v>
-      </c>
       <c r="F6" t="n">
-        <v>75.3</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>13.6</v>
+        <v>72</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>15.9</v>
       </c>
       <c r="I6" t="n">
-        <v>23.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K6" t="n">
         <v>100</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.5113</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0251</v>
+        <v>0.8016</v>
       </c>
       <c r="M6" t="n">
-        <v>12.4</v>
+        <v>0.0253</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="b">
+        <v>-1.5</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>oracle: cheapest-pass</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>27</v>
-      </c>
       <c r="F7" t="n">
-        <v>60.5</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2</v>
+        <v>58.3</v>
       </c>
       <c r="H7" t="n">
-        <v>-13.6</v>
+        <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>9.9</v>
+        <v>-6.8</v>
       </c>
       <c r="J7" t="n">
-        <v>-9</v>
+        <v>11.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4686</v>
+        <v>14</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0287</v>
+        <v>0.7466</v>
       </c>
       <c r="M7" t="n">
-        <v>28.3</v>
+        <v>0.0291</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="b">
+        <v>13.2</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>learned: k-NN on task text (TF-IDF)</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>27</v>
-      </c>
       <c r="F8" t="n">
-        <v>55.6</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.2</v>
+        <v>50.8</v>
       </c>
       <c r="H8" t="n">
-        <v>-13.6</v>
+        <v>-5.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>-45</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3888</v>
+        <v>-33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0259</v>
+        <v>0.822</v>
       </c>
       <c r="M8" t="n">
-        <v>15.9</v>
+        <v>0.0368</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="b">
+        <v>43.2</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>learned: decision tree on metadata</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>27</v>
-      </c>
       <c r="F9" t="n">
-        <v>61.7</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.9</v>
+        <v>-3</v>
       </c>
       <c r="I9" t="n">
-        <v>9.9</v>
+        <v>-11.4</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3815</v>
+        <v>-19</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0229</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4</v>
+        <v>0.0278</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>cache: lookup (k-fold, honest)</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
-        <v>27</v>
-      </c>
       <c r="F10" t="n">
-        <v>64.2</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>58.3</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5</v>
+        <v>2.3</v>
       </c>
       <c r="I10" t="n">
-        <v>8.6</v>
+        <v>-2.3</v>
       </c>
       <c r="J10" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3288</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>0.019</v>
+        <v>0.5952</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.2</v>
+        <v>0.0232</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="b">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>router: jev (no training)</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>5</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>27</v>
-      </c>
       <c r="F11" t="n">
-        <v>56.8</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9</v>
+        <v>51.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-16</v>
+        <v>-4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>7.4</v>
+        <v>-14.4</v>
       </c>
       <c r="J11" t="n">
-        <v>-36</v>
+        <v>6.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5459000000000001</v>
+        <v>-26</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0356</v>
+        <v>0.9479</v>
       </c>
       <c r="M11" t="n">
-        <v>59.2</v>
+        <v>0.0415</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1699</v>
-      </c>
-      <c r="O11" t="b">
-        <v>0</v>
+        <v>61.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.2805</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>router: luna-profiles (no training)</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>27</v>
-      </c>
       <c r="F12" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7</v>
+        <v>54.2</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.6</v>
+        <v>-1.9</v>
       </c>
       <c r="I12" t="n">
-        <v>8.6</v>
+        <v>-11.4</v>
       </c>
       <c r="J12" t="n">
-        <v>-27</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4037</v>
+        <v>-12</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0258</v>
+        <v>0.8243</v>
       </c>
       <c r="M12" t="n">
-        <v>15.2</v>
+        <v>0.0346</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0199</v>
-      </c>
-      <c r="O12" t="b">
-        <v>0</v>
+        <v>34.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0331</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>router: luna-cards (no training)</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>27</v>
-      </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.7</v>
+        <v>53.4</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.1</v>
+        <v>-2.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>-6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>-27</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3808</v>
+        <v>-17</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0243</v>
+        <v>0.6694</v>
       </c>
       <c r="M13" t="n">
-        <v>8.699999999999999</v>
+        <v>0.0285</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0041</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
+        <v>10.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0068</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>always terminus-2</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>27</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>60.5</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="H14" t="n">
-        <v>-4.9</v>
+        <v>-1.2</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="K14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L14" t="n">
         <v>0.6791</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0.0416</v>
       </c>
-      <c r="M14" t="n">
-        <v>0.4</v>
-      </c>
       <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="b">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>always mini-swe-agent</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>27</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>61.7</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H15" t="n">
-        <v>-4.9</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>0.3727</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.0224</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-46</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="b">
+      <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>always pi</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>27</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>54.3</v>
       </c>
-      <c r="G16" t="n">
-        <v>-4.9</v>
-      </c>
       <c r="H16" t="n">
-        <v>-18.5</v>
+        <v>-7.4</v>
       </c>
       <c r="I16" t="n">
-        <v>8.6</v>
+        <v>-21</v>
       </c>
       <c r="J16" t="n">
-        <v>-31</v>
+        <v>7.4</v>
       </c>
       <c r="K16" t="n">
+        <v>-55</v>
+      </c>
+      <c r="L16" t="n">
         <v>0.3137</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>0.0214</v>
       </c>
-      <c r="M16" t="n">
-        <v>-48.3</v>
-      </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="b">
+        <v>-4.4</v>
+      </c>
+      <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>random</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>27</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>58.8</v>
       </c>
-      <c r="G17" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="H17" t="n">
-        <v>-6.6</v>
+        <v>-2.9</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>-9.9</v>
       </c>
       <c r="J17" t="n">
-        <v>-3</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L17" t="n">
         <v>0.4552</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>0.0286</v>
       </c>
-      <c r="M17" t="n">
-        <v>-30.8</v>
-      </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="b">
+        <v>28.1</v>
+      </c>
+      <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>perfect picking</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>27</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>75.3</v>
       </c>
-      <c r="G18" t="n">
-        <v>16</v>
-      </c>
       <c r="H18" t="n">
-        <v>7.4</v>
+        <v>13.6</v>
       </c>
       <c r="I18" t="n">
-        <v>24.7</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K18" t="n">
         <v>100</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>0.5113</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>0.0251</v>
       </c>
-      <c r="M18" t="n">
-        <v>-39.3</v>
-      </c>
       <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="b">
+        <v>12.4</v>
+      </c>
+      <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>oracle: cheapest-pass</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>27</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>60.5</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="H19" t="n">
-        <v>-11.1</v>
+        <v>-1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>12.3</v>
+        <v>-13.6</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="K19" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L19" t="n">
         <v>0.4686</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0.0287</v>
       </c>
-      <c r="M19" t="n">
-        <v>-30.7</v>
-      </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="b">
+        <v>28.3</v>
+      </c>
+      <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>learned: k-NN on task text (TF-IDF)</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>27</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>55.6</v>
       </c>
-      <c r="G20" t="n">
-        <v>-3.7</v>
-      </c>
       <c r="H20" t="n">
-        <v>-12.3</v>
+        <v>-6.2</v>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>-13.6</v>
       </c>
       <c r="J20" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>-45</v>
+      </c>
+      <c r="L20" t="n">
         <v>0.3888</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.0259</v>
       </c>
-      <c r="M20" t="n">
-        <v>-37.4</v>
-      </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="b">
+        <v>15.9</v>
+      </c>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>learned: decision tree on metadata</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>27</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>61.7</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H21" t="n">
-        <v>-7.4</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>13.6</v>
+        <v>-9.9</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>9.9</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>0.3815</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.0229</v>
       </c>
-      <c r="M21" t="n">
-        <v>-44.7</v>
-      </c>
       <c r="N21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="b">
+      <c r="P21" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
-        <v>1</v>
+      <c r="Q21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>cache: lookup (k-fold, honest)</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>27</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>64.2</v>
       </c>
-      <c r="G22" t="n">
-        <v>4.9</v>
-      </c>
       <c r="H22" t="n">
-        <v>-3.7</v>
+        <v>2.5</v>
       </c>
       <c r="I22" t="n">
-        <v>14.8</v>
+        <v>-2.5</v>
       </c>
       <c r="J22" t="n">
-        <v>31</v>
+        <v>8.6</v>
       </c>
       <c r="K22" t="n">
+        <v>18</v>
+      </c>
+      <c r="L22" t="n">
         <v>0.3288</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0.019</v>
       </c>
-      <c r="M22" t="n">
-        <v>-54.2</v>
-      </c>
       <c r="N22" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="b">
+      <c r="P22" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
-        <v>1</v>
+      <c r="Q22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>router: jev (no training)</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>27</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>56.8</v>
       </c>
-      <c r="G23" t="n">
-        <v>-2.5</v>
-      </c>
       <c r="H23" t="n">
-        <v>-13.6</v>
+        <v>-4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>9.9</v>
+        <v>-16</v>
       </c>
       <c r="J23" t="n">
-        <v>-15</v>
+        <v>7.4</v>
       </c>
       <c r="K23" t="n">
+        <v>-36</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.5459000000000001</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>0.0356</v>
       </c>
-      <c r="M23" t="n">
-        <v>-14</v>
-      </c>
       <c r="N23" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.1699</v>
-      </c>
-      <c r="O23" t="b">
-        <v>0</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
       </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>router: luna-profiles (no training)</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>27</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>58</v>
       </c>
-      <c r="G24" t="n">
-        <v>-1.2</v>
-      </c>
       <c r="H24" t="n">
-        <v>-12.3</v>
+        <v>-3.7</v>
       </c>
       <c r="I24" t="n">
-        <v>9.9</v>
+        <v>-13.6</v>
       </c>
       <c r="J24" t="n">
-        <v>-8</v>
+        <v>8.6</v>
       </c>
       <c r="K24" t="n">
+        <v>-27</v>
+      </c>
+      <c r="L24" t="n">
         <v>0.4037</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>0.0258</v>
       </c>
-      <c r="M24" t="n">
-        <v>-37.8</v>
-      </c>
       <c r="N24" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.0199</v>
       </c>
-      <c r="O24" t="b">
+      <c r="P24" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
-        <v>1</v>
+      <c r="Q24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>router: luna-cards (no training)</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>27</v>
+      </c>
+      <c r="G25" t="n">
+        <v>58</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-27</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="P25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>always terminus-2</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>27</v>
+      </c>
+      <c r="G26" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6791</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>always mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>27</v>
+      </c>
+      <c r="G27" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-46</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>always pi</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-31</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>27</v>
+      </c>
+      <c r="G29" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>perfect picking</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>27</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>100</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oracle: cheapest-pass</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>27</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-30.7</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>learned: k-NN on task text (TF-IDF)</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>27</v>
+      </c>
+      <c r="G32" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-23</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-37.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>learned: decision tree on metadata</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>27</v>
+      </c>
+      <c r="G33" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>15</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-44.7</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>cache: lookup (k-fold, honest)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>27</v>
+      </c>
+      <c r="G34" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>31</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-54.2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>router: jev (no training)</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>27</v>
+      </c>
+      <c r="G35" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.5459000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-14</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>router: luna-profiles (no training)</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>27</v>
+      </c>
+      <c r="G36" t="n">
+        <v>58</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-37.8</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="P36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>router: luna-cards (no training)</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F37" t="n">
         <v>27</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G37" t="n">
         <v>58</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H37" t="n">
         <v>-1.2</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I37" t="n">
         <v>-11.1</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J37" t="n">
         <v>8.6</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K37" t="n">
         <v>-8</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L37" t="n">
         <v>0.3808</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M37" t="n">
         <v>0.0243</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N37" t="n">
         <v>-41.3</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O37" t="n">
         <v>0.0041</v>
       </c>
-      <c r="O25" t="b">
+      <c r="P37" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
+      <c r="Q37" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P25"/>
+  <autoFilter ref="A1:Q37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>tasks</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>pass_rate_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>diff_vs_reference_pts</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>ci95_low</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>ci95_high</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>cost_per_pass_usd</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>tasks_diverted_from_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. lookup vs oracle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>all 45 Luna tasks</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>stable oracle (best of 3 harnesses)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. lookup vs oracle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>all 45 Luna tasks</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>lookup, all 45 tasks hard-coded</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>equals the oracle by construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1. lookup vs oracle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>all 45 Luna tasks</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lookup, development tasks only (previous)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E4" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. lookup vs oracle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all 45 Luna tasks</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>always mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E5" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1. lookup vs oracle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18 test tasks only</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>stable oracle (best of 3 harnesses)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>63</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1. lookup vs oracle</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18 test tasks only</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>lookup, all 45 tasks hard-coded</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>63</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>equals the oracle by construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1. lookup vs oracle</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18 test tasks only</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>lookup, development tasks only (previous)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. lookup vs oracle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18 test tasks only</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>always mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Qwen PASS</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Qwen FAIL</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>terminus-2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Qwen gave no signal</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Qwen PASS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Qwen FAIL</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>27</v>
+      </c>
+      <c r="E14" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>mini-swe-agent</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Qwen gave no signal</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Qwen PASS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Qwen FAIL</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E17" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Qwen gave no signal</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Luna pass rate on those tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>best-harness hit rate</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Qwen passed with any harness</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>21</v>
+      </c>
+      <c r="E19" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>16/21 are Luna's best harness; 33.3% by chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>best-harness hit rate</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Qwen passed with exactly one harness</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6/11 are Luna's best harness; 33.3% by chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2. does Qwen predict Luna</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pooled over harness-task pairs</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Luna pass rate, Qwen PASS minus Qwen FAIL</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>points; Qwen carries real signal about Luna</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fixed default, all 45 tasks</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>always the best single harness</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>best by the CI rule</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fixed default, all 45 tasks</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>first Qwen pass in a fixed order (current)</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" t="n">
+        <v>57</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>the rule lookup() uses (by decision; CI includes 0)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fixed default, all 45 tasks</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>divert from default only if Qwen failed it</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>45</v>
+      </c>
+      <c r="E24" t="n">
+        <v>57</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fixed default, all 45 tasks</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>best-ranked harness among Qwen passes</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>57</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fixed default, 21 tasks Qwen could act on</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>always the best single harness</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>21</v>
+      </c>
+      <c r="E26" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>best by the CI rule</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fixed default, 21 tasks Qwen could act on</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>first Qwen pass in a fixed order (current)</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>21</v>
+      </c>
+      <c r="E27" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>the rule lookup() uses (by decision; CI includes 0)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fixed default, 21 tasks Qwen could act on</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>divert from default only if Qwen failed it</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>21</v>
+      </c>
+      <c r="E28" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fixed default, 21 tasks Qwen could act on</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>best-ranked harness among Qwen passes</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>21</v>
+      </c>
+      <c r="E29" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>loto default, all 45 tasks</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>always the best single harness</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>45</v>
+      </c>
+      <c r="E30" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>unstable reference, sensitivity check only</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0397</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>loto default, all 45 tasks</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>first Qwen pass in a fixed order (current)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>45</v>
+      </c>
+      <c r="E31" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>unstable reference, sensitivity check only</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>17</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="K31" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>loto default, all 45 tasks</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>divert from default only if Qwen failed it</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>45</v>
+      </c>
+      <c r="E32" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>unstable reference, sensitivity check only</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loto default, all 45 tasks</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>best-ranked harness among Qwen passes</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>unstable reference, sensitivity check only</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="K33" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loto default, 21 tasks Qwen could act on</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>always the best single harness</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>21</v>
+      </c>
+      <c r="E34" t="n">
+        <v>54</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>unstable reference, sensitivity check only</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>loto default, 21 tasks Qwen could act on</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>first Qwen pass in a fixed order (current)</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>21</v>
+      </c>
+      <c r="E35" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>unstable reference, sensitivity check only</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="K35" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>loto default, 21 tasks Qwen could act on</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>divert from default only if Qwen failed it</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>21</v>
+      </c>
+      <c r="E36" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>unstable reference, sensitivity check only</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3. fallback rules</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>loto default, 21 tasks Qwen could act on</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>best-ranked harness among Qwen passes</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>21</v>
+      </c>
+      <c r="E37" t="n">
+        <v>73</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>unstable reference, sensitivity check only</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>19</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K37"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -58029,7 +62175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -63447,7 +67593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -78014,263 +82160,4 @@
   <autoFilter ref="A1:J361"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>harness</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>error_type</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>attempts_failed</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>share_of_harness_attempts_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mini-swe-agent</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AgentSetupTimeoutError</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mini-swe-agent</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NonZeroAgentExitCodeError</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mini-swe-agent</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RuntimeError</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>pi</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NonZeroAgentExitCodeError</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>pi</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>RuntimeError</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>pi</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>VerifierTimeoutError</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>terminus-2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>APIError</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>terminus-2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RuntimeError</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>11</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>terminus-2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VerifierTimeoutError</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>terminus-2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TOTAL (any error)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>13</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>mini-swe-agent</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TOTAL (any error)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>21</v>
-      </c>
-      <c r="D12" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pi</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TOTAL (any error)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>17</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D13"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>